--- a/03_Outputs/Rio_Grande/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Rio_Grande/02_Demografia/demografia.xlsx
@@ -112,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -181,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,19 +717,19 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,29 +1205,29 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>Población total</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>Densidad poblacional (hab/km²)</t>
         </is>
@@ -1187,185 +1325,185 @@
   <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1390,91 +1528,91 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>3251</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>3185</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>984</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>1116</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>927</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>930</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>948</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>642</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>473</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>285</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>131</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>491</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>570</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>481</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>458</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>495</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>313</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>247</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>126</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>70</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>493</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>546</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>446</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>472</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>453</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>329</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>226</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>159</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>61</v>
       </c>
     </row>
@@ -1497,91 +1635,91 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>9533</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>10965</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>2828</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>3114</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>3192</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>3207</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>2756</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>2218</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>1805</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>967</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>411</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>1506</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>1488</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>1497</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>1499</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>1265</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>961</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>743</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>409</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>165</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>1322</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>1626</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>1695</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>1708</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>1491</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>1257</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>1062</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>558</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>246</v>
       </c>
     </row>
@@ -1604,91 +1742,91 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>6038</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>6120</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>1801</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>1837</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>1875</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>1974</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>1809</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>1236</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>969</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>471</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>186</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>853</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>899</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>962</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>986</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>944</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>620</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>457</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>221</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>96</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>948</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>938</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>913</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>988</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>865</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>616</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>512</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>250</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>90</v>
       </c>
     </row>
@@ -1711,91 +1849,91 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>11417</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>12334</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>3271</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>3571</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>3754</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>3810</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>3412</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>2602</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>1933</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>998</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>400</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>1639</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>1786</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>1857</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>1849</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>1619</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>1205</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>881</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>429</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>152</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>1632</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>1785</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>1897</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>1961</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>1793</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>1397</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>1052</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>569</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>248</v>
       </c>
     </row>
@@ -1818,200 +1956,200 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>19479</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>19861</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>5895</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>6244</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>6436</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>6308</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>5370</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>3895</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>2959</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>1632</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>601</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>2968</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>3126</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>3319</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>3178</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>2625</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>1851</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>1438</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>727</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>247</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>2927</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>3118</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>3117</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>3130</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>2745</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>2044</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>1521</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>905</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>354</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="23">
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="26">
         <v>49718</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="28">
         <v>52465</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="30">
         <v>14779</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="32">
         <v>15882</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="34">
         <v>16184</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="36">
         <v>16229</v>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="38">
         <v>14295</v>
       </c>
-      <c r="L7" s="37">
+      <c r="L7" s="40">
         <v>10593</v>
       </c>
-      <c r="M7" s="39">
+      <c r="M7" s="42">
         <v>8139</v>
       </c>
-      <c r="N7" s="41">
+      <c r="N7" s="44">
         <v>4353</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="46">
         <v>1729</v>
       </c>
-      <c r="P7" s="45">
+      <c r="P7" s="48">
         <v>7457</v>
       </c>
-      <c r="Q7" s="47">
+      <c r="Q7" s="50">
         <v>7869</v>
       </c>
-      <c r="R7" s="49">
+      <c r="R7" s="52">
         <v>8116</v>
       </c>
-      <c r="S7" s="51">
+      <c r="S7" s="54">
         <v>7970</v>
       </c>
-      <c r="T7" s="53">
+      <c r="T7" s="56">
         <v>6948</v>
       </c>
-      <c r="U7" s="55">
+      <c r="U7" s="58">
         <v>4950</v>
       </c>
-      <c r="V7" s="57">
+      <c r="V7" s="60">
         <v>3766</v>
       </c>
-      <c r="W7" s="59">
+      <c r="W7" s="62">
         <v>1912</v>
       </c>
-      <c r="X7" s="61">
+      <c r="X7" s="64">
         <v>730</v>
       </c>
-      <c r="Y7" s="63">
+      <c r="Y7" s="66">
         <v>7322</v>
       </c>
-      <c r="Z7" s="65">
+      <c r="Z7" s="68">
         <v>8013</v>
       </c>
-      <c r="AA7" s="67">
+      <c r="AA7" s="70">
         <v>8068</v>
       </c>
-      <c r="AB7" s="69">
+      <c r="AB7" s="72">
         <v>8259</v>
       </c>
-      <c r="AC7" s="71">
+      <c r="AC7" s="74">
         <v>7347</v>
       </c>
-      <c r="AD7" s="73">
+      <c r="AD7" s="76">
         <v>5643</v>
       </c>
-      <c r="AE7" s="75">
+      <c r="AE7" s="78">
         <v>4373</v>
       </c>
-      <c r="AF7" s="77">
+      <c r="AF7" s="80">
         <v>2441</v>
       </c>
-      <c r="AG7" s="79">
+      <c r="AG7" s="82">
         <v>999</v>
       </c>
     </row>
@@ -2027,47 +2165,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -2092,14 +2230,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>6.17986664498292</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>4.68270628128532</v>
       </c>
-      <c r="G2" s="84">
-        <v>25.3469387755102</v>
+      <c r="G2" s="90">
+        <v>24.603515625</v>
       </c>
     </row>
     <row r="3">
@@ -2121,14 +2259,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>8.51128892513124</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>5.4852963583727</v>
       </c>
-      <c r="G3" s="84">
-        <v>28.665785997358</v>
+      <c r="G3" s="90">
+        <v>26.5109329223633</v>
       </c>
     </row>
     <row r="4">
@@ -2150,14 +2288,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>6.8837058632977</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>3.42138765117759</v>
       </c>
-      <c r="G4" s="84">
-        <v>24.6845606790548</v>
+      <c r="G4" s="90">
+        <v>22.5043411254883</v>
       </c>
     </row>
     <row r="5">
@@ -2179,14 +2317,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>12.3257585944153</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>6.05462618289456</v>
       </c>
-      <c r="G5" s="84">
-        <v>26.6380236305048</v>
+      <c r="G5" s="90">
+        <v>24.4525547027588</v>
       </c>
     </row>
     <row r="6">
@@ -2208,107 +2346,107 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>7.9159030747302</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>4.3731778425656</v>
       </c>
-      <c r="G6" s="84">
-        <v>24.8190061151332</v>
+      <c r="G6" s="90">
+        <v>23.8943023681641</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por población)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="81">
+      <c r="C7" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="87">
         <v>8.76786595397339</v>
       </c>
-      <c r="F7" s="83">
+      <c r="F7" s="89">
         <v>4.85988616924724</v>
       </c>
-      <c r="G7" s="85">
-        <v>25.9868131872283</v>
+      <c r="G7" s="91">
+        <v>24.3970542026017</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="81">
+      <c r="C8" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="87">
         <v>7.88520580382868</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="89">
         <v>5.13999885007764</v>
       </c>
-      <c r="G8" s="85">
-        <v>26.3837840326381</v>
+      <c r="G8" s="91">
+        <v>24.6272584356484</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="81">
+      <c r="C9" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F9" s="83">
+      <c r="F9" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G9" s="85">
-        <v>32.052654940463</v>
+      <c r="G9" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -2323,47 +2461,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -2388,13 +2526,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>0.571446725081086</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>0</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>0.839989681918452</v>
       </c>
     </row>
@@ -2417,13 +2555,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>4.03759889426787</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>4.60105120017657</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>2.84424205001544</v>
       </c>
     </row>
@@ -2446,13 +2584,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>1.18043882640778</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>0.878385180710763</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>1.55361032674466</v>
       </c>
     </row>
@@ -2475,13 +2613,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>3.08887062941456</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>2.82540653973723</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>3.47365447701455</v>
       </c>
     </row>
@@ -2504,106 +2642,106 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>1.57637475331314</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>0</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>3.90121791795219</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA DEL RÍO GRANDE (por población)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="87">
+      <c r="C7" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="96">
         <v>2.27973798034388</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="98">
         <v>1.63221199290464</v>
       </c>
-      <c r="G7" s="91">
+      <c r="G7" s="100">
         <v>3.11903734613696</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="87">
+      <c r="C8" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="96">
         <v>1.82462249111888</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="98">
         <v>1.50531530154741</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="100">
         <v>2.24897326039897</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="87">
+      <c r="C9" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -2619,23 +2757,23 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -2718,35 +2856,35 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -2859,22 +2997,23 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -2957,23 +3096,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -3261,17 +3400,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -3284,7 +3423,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>25.3469387755102</v>
+        <v>24.603515625</v>
       </c>
     </row>
     <row r="3">
@@ -3294,7 +3433,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>28.665785997358</v>
+        <v>26.5109329223633</v>
       </c>
     </row>
     <row r="4">
@@ -3304,7 +3443,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>24.6845606790548</v>
+        <v>22.5043411254883</v>
       </c>
     </row>
     <row r="5">
@@ -3314,7 +3453,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>26.6380236305048</v>
+        <v>24.4525547027588</v>
       </c>
     </row>
     <row r="6">
@@ -3324,7 +3463,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>24.8190061151332</v>
+        <v>23.8943023681641</v>
       </c>
     </row>
   </sheetData>
